--- a/data/trans_orig/IP16_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Estudios-trans_orig.xlsx
@@ -988,12 +988,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36160</t>
+          <t>37086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54383</t>
+          <t>54250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>75086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53705</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>42977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>86633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107140</t>
+          <t>107743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>62757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81377</t>
+          <t>80424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107015</t>
+          <t>107373</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76068</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94551</t>
+          <t>94759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>149904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176572</t>
+          <t>177095</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79844</t>
+          <t>80295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148710</t>
+          <t>147743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166219</t>
+          <t>165578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5327,12 +5327,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34381</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>59578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5888,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7098,12 +7098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>65858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136075</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151035</t>
+          <t>151445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -8357,12 +8357,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>28182</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8407,47 +8407,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>50806</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>45938</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>54213</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>79,67%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>50806</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>46038</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>54163</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10382,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10397,12 +10397,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>16088</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>35875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42575</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77302</t>
+          <t>76889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75733</t>
+          <t>75742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>104531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86947</t>
+          <t>86403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151185</t>
+          <t>151243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190711</t>
+          <t>193502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -11054,12 +11054,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11124,12 +11124,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -11165,12 +11165,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11180,12 +11180,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11311,12 +11311,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65615</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11615,12 +11615,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11726,12 +11726,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -11837,12 +11837,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106002</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11922,12 +11922,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -11948,12 +11948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -943,92 +943,92 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>25,96%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1054,72 +1054,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7342</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3878</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10981</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4213</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8118</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -1165,72 +1165,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16774</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>14706</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11067</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18170</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10565</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18074</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14001</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9786</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16963</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>33219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -1278,57 +1278,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1504,72 +1504,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>517</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3196</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2959</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1615,72 +1615,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4675</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8569</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8817</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,79%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4065</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1726,72 +1726,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28701</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43419</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29048</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22546</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37086</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22165</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35576</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29153</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>43396</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75086</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -1837,72 +1837,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50765</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43132</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57529</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46467</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38340</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>53245</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39601</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>50765</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>42977</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>57661</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86633</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107743</t>
+          <t>106782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -1950,57 +1950,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2292,59 +2292,59 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4735</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -2398,72 +2398,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8131</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17562</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>5217</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2541</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8956</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>23,13%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>8403</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>17740</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -2509,72 +2509,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21163</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16235</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>25966</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>73,63%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>16197</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>12602</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19288</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12796</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>19220</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>71,82%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>21163</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>16092</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>25466</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42572</t>
+          <t>42926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2622,57 +2622,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2848,72 +2848,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>517</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2959,72 +2959,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4697</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>5813</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10045</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>11026</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>4697</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>9419</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3070,72 +3070,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>52567</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>44614</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>62820</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>41607</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>34063</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>50655</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>33276</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>50792</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>27,18%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>52567</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>44522</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>62757</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>36,71%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80424</t>
+          <t>81635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107373</t>
+          <t>107585</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -3181,72 +3181,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>85930</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>76072</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>95079</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>60,01%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>77368</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>68180</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>85591</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>68250</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>86190</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>61,74%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>85930</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>77038</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>94759</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>149904</t>
+          <t>150275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177095</t>
+          <t>175780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -3294,57 +3294,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3474,7 +3474,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3862,84 +3862,84 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -3973,72 +3973,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5053</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2509</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8519</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -4084,72 +4084,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12935</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17529</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18008</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14542</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20552</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20562</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>16293</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13572</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17531</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37559</t>
+          <t>37441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -4197,57 +4197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>23061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>23061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4534,72 +4534,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>3714</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1331</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8866</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -4645,72 +4645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14427</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9620</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21834</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12870</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7836</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19111</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19817</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>14,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14427</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9098</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -4756,72 +4756,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>79200</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91414</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>64190</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76832</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>63855</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86607</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80295</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>91936</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147743</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165578</t>
+          <t>166451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -4869,57 +4869,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5095,84 +5095,84 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>1097</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4931</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5317,72 +5317,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4505</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1776</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8859</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4833</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9270</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9146</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4505</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8581</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -5428,72 +5428,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>33830</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28804</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>36770</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>31571</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27134</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34287</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>27258</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>34091</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>86,72%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>74,54%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>33830</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>29579</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>37018</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>85,79%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59578</t>
+          <t>59452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -5541,57 +5541,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5767,84 +5767,84 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>1097</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5834</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5878,72 +5878,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>3714</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>8509</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8471</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>4389</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -5958,12 +5958,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20140</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13966</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>28287</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>22757</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>15851</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>31045</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>16179</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>31310</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>15,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>14203</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>28244</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>54784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -6100,72 +6100,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>136730</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>128533</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>143317</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>121231</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>112361</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>128797</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>112881</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>128309</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>136730</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>128420</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>143251</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,22%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246197</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>268565</t>
+          <t>268062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -6213,57 +6213,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6382,7 +6382,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6393,7 +6393,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6892,64 +6892,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -7003,74 +7003,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15127</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13242</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7385</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -7083,12 +7083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7098,12 +7098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -7116,57 +7116,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7458,59 +7458,59 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2759</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2961</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7564,72 +7564,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12289</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7607</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18363</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10673</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6528</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16991</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16011</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12289</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7693</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17892</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -7675,72 +7675,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72662</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66579</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77822</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>71770</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65858</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76031</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>66380</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>76116</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72662</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67045</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77277</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151445</t>
+          <t>150927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -7788,57 +7788,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8125,84 +8125,84 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -8236,72 +8236,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>17,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4216</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8306</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8444</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>14,64%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -8352,67 +8352,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>26232</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23086</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>28218</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>24576</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>20486</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>26886</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>20348</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>27062</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>85,36%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>26232</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>28182</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -8460,57 +8460,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8797,64 +8797,64 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>4272</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -8913,67 +8913,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>15616</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>10544</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>22093</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>15454</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9970</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>21752</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>9543</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>21878</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>12,12%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>15616</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>10674</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>22777</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>22960</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>39927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -9019,72 +9019,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>106278</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>99367</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>111756</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>111472</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>104797</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>117068</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>104794</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>82,22%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>106278</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>98885</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>111791</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>207826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225537</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -9132,57 +9132,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9301,7 +9301,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -9312,7 +9312,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -9589,82 +9589,82 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3742</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>897</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -9700,47 +9700,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4333</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9775,32 +9775,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -9811,72 +9811,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6597</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9886,32 +9886,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -9922,72 +9922,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5372</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11616</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12965</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9647</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9997,32 +9997,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -10035,57 +10035,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10261,72 +10261,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -10377,32 +10377,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10412,32 +10412,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -10483,72 +10483,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33854</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26555</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43381</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12404</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35875</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>30617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10558,32 +10558,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>58066</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38839</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76889</t>
+          <t>69766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -10594,72 +10594,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70571</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>78388</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>88644</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75742</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>104531</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78234</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68650</t>
+          <t>53856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86403</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10669,32 +10669,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>166878</t>
+          <t>132069</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>119913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193502</t>
+          <t>143051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -10707,57 +10707,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10822,72 +10822,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>867</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -11044,72 +11044,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9374</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,74%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11119,32 +11119,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -11155,72 +11155,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8656</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14537</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12904</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>8596</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18207</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30,99%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>43,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -11240,22 +11240,22 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -11271,32 +11271,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29875</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11306,32 +11306,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38080</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11341,32 +11341,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65082</t>
+          <t>61584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -11379,57 +11379,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11454,17 +11454,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11494,72 +11494,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>541</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -11605,72 +11605,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6812</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11680,32 +11680,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -11721,32 +11721,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -11827,72 +11827,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>46144</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>36649</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>56182</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>39347</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>23374</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>50843</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>50508</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40349</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61815</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11902,32 +11902,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>89856</t>
+          <t>84479</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69490</t>
+          <t>72081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107821</t>
+          <t>97770</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -11938,72 +11938,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>108997</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>98324</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>118819</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>59,61%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>127052</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>113248</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>147134</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>120997</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109441</t>
+          <t>84681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>102748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>229557</t>
+          <t>187066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>273932</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -12051,57 +12051,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12126,17 +12126,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
